--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17302-2026 artfynd.xlsx
+++ b/artfynd/A 17302-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136949790</v>
       </c>
       <c r="B2" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136949791</v>
       </c>
       <c r="B3" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136949792</v>
       </c>
       <c r="B4" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136949793</v>
       </c>
       <c r="B5" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
